--- a/Analysis/competitive_baselines.xlsx
+++ b/Analysis/competitive_baselines.xlsx
@@ -10,6 +10,7 @@
     <sheet name="AE_vs_FixedDefault" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="SingleCriterionArgmax" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="BestSingleCriterion" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="PairedTests_AE_vs_baselines" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -415,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N17"/>
+  <dimension ref="A1:T17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,22 +472,52 @@
       </c>
       <c r="K1" t="inlineStr">
         <is>
+          <t>NN_tau</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>NN_top1</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
           <t>d_tau</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>d_top1</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>AE_beats_FD_tau</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>AE_beats_FD_top1</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>d_tau_NN</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>d_top1_NN</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>AE_beats_NN_tau</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>AE_beats_NN_top1</t>
         </is>
       </c>
     </row>
@@ -505,36 +536,54 @@
         <v>5</v>
       </c>
       <c r="D2" t="n">
-        <v>0.30668</v>
+        <v>0.253</v>
       </c>
       <c r="E2" t="n">
-        <v>0.03565917834162757</v>
+        <v>0.03731306741612112</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5353800000000001</v>
+        <v>0.48308</v>
       </c>
       <c r="G2" t="n">
-        <v>0.03298214668574501</v>
+        <v>0.01826190022971324</v>
       </c>
       <c r="H2" t="n">
-        <v>195</v>
+        <v>194.8</v>
       </c>
       <c r="I2" t="n">
-        <v>0.6137</v>
+        <v>0.5795</v>
       </c>
       <c r="J2" t="n">
-        <v>0.7026</v>
+        <v>0.6359</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.3070200000000001</v>
+        <v>0.3744</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.1672199999999999</v>
-      </c>
-      <c r="M2" t="b">
-        <v>0</v>
-      </c>
-      <c r="N2" t="b">
+        <v>0.6462</v>
+      </c>
+      <c r="M2" t="n">
+        <v>-0.3265</v>
+      </c>
+      <c r="N2" t="n">
+        <v>-0.15282</v>
+      </c>
+      <c r="O2" t="b">
+        <v>0</v>
+      </c>
+      <c r="P2" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>-0.1214</v>
+      </c>
+      <c r="R2" t="n">
+        <v>-0.16312</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="b">
         <v>0</v>
       </c>
     </row>
@@ -553,36 +602,54 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.04188</v>
+        <v>0.03046</v>
       </c>
       <c r="E3" t="n">
-        <v>0.04074711032699129</v>
+        <v>0.1125714128897741</v>
       </c>
       <c r="F3" t="n">
-        <v>0.32856</v>
+        <v>0.29716</v>
       </c>
       <c r="G3" t="n">
-        <v>0.03640896867531405</v>
+        <v>0.05380825215522243</v>
       </c>
       <c r="H3" t="n">
         <v>70</v>
       </c>
       <c r="I3" t="n">
-        <v>0.9333</v>
+        <v>0.7905</v>
       </c>
       <c r="J3" t="n">
-        <v>0.9571</v>
+        <v>0.7714</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.89142</v>
+        <v>0.181</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.6285399999999999</v>
-      </c>
-      <c r="M3" t="b">
-        <v>0</v>
-      </c>
-      <c r="N3" t="b">
+        <v>0.5143</v>
+      </c>
+      <c r="M3" t="n">
+        <v>-0.7600399999999999</v>
+      </c>
+      <c r="N3" t="n">
+        <v>-0.4742399999999999</v>
+      </c>
+      <c r="O3" t="b">
+        <v>0</v>
+      </c>
+      <c r="P3" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>-0.15054</v>
+      </c>
+      <c r="R3" t="n">
+        <v>-0.2171399999999999</v>
+      </c>
+      <c r="S3" t="b">
+        <v>0</v>
+      </c>
+      <c r="T3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -601,37 +668,55 @@
         <v>5</v>
       </c>
       <c r="D4" t="n">
-        <v>0.41744</v>
+        <v>0.2872</v>
       </c>
       <c r="E4" t="n">
-        <v>0.06379108871935014</v>
+        <v>0.03837538273424775</v>
       </c>
       <c r="F4" t="n">
-        <v>0.70152</v>
+        <v>0.6</v>
       </c>
       <c r="G4" t="n">
-        <v>0.06489327391956734</v>
+        <v>0.02434953798329651</v>
       </c>
       <c r="H4" t="n">
-        <v>65</v>
+        <v>64.8</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0974</v>
+        <v>0.1795</v>
       </c>
       <c r="J4" t="n">
-        <v>0.2923</v>
+        <v>0.3231</v>
       </c>
       <c r="K4" t="n">
-        <v>0.32004</v>
+        <v>0.4667</v>
       </c>
       <c r="L4" t="n">
-        <v>0.40922</v>
-      </c>
-      <c r="M4" t="b">
+        <v>0.7231</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.1077</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.2769</v>
+      </c>
+      <c r="O4" t="b">
         <v>1</v>
       </c>
-      <c r="N4" t="b">
+      <c r="P4" t="b">
         <v>1</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>-0.1795</v>
+      </c>
+      <c r="R4" t="n">
+        <v>-0.1231</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -649,36 +734,54 @@
         <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>0.49558</v>
+        <v>0.4755599999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1031983623901077</v>
+        <v>0.02875870303056102</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5966799999999999</v>
+        <v>0.5733600000000001</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0447288162150531</v>
+        <v>0.03836375893991618</v>
       </c>
       <c r="H5" t="n">
         <v>60</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8</v>
+        <v>0.7667</v>
       </c>
       <c r="J5" t="n">
-        <v>0.85</v>
+        <v>0.8167</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.30442</v>
+        <v>0.5</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.2533200000000001</v>
-      </c>
-      <c r="M5" t="b">
-        <v>0</v>
-      </c>
-      <c r="N5" t="b">
+        <v>0.7167</v>
+      </c>
+      <c r="M5" t="n">
+        <v>-0.2911400000000001</v>
+      </c>
+      <c r="N5" t="n">
+        <v>-0.2433399999999999</v>
+      </c>
+      <c r="O5" t="b">
+        <v>0</v>
+      </c>
+      <c r="P5" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>-0.02444000000000007</v>
+      </c>
+      <c r="R5" t="n">
+        <v>-0.1433399999999999</v>
+      </c>
+      <c r="S5" t="b">
+        <v>0</v>
+      </c>
+      <c r="T5" t="b">
         <v>0</v>
       </c>
     </row>
@@ -697,36 +800,54 @@
         <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>0.30986</v>
+        <v>0.29846</v>
       </c>
       <c r="E6" t="n">
-        <v>0.01874601290941624</v>
+        <v>0.008163516399199553</v>
       </c>
       <c r="F6" t="n">
-        <v>0.48708</v>
+        <v>0.4748599999999999</v>
       </c>
       <c r="G6" t="n">
-        <v>0.01996163820932541</v>
+        <v>0.01124201939155063</v>
       </c>
       <c r="H6" t="n">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6137</v>
+        <v>0.5795</v>
       </c>
       <c r="J6" t="n">
-        <v>0.7026</v>
+        <v>0.6359</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.30384</v>
+        <v>0.3744</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.21552</v>
-      </c>
-      <c r="M6" t="b">
-        <v>0</v>
-      </c>
-      <c r="N6" t="b">
+        <v>0.6462</v>
+      </c>
+      <c r="M6" t="n">
+        <v>-0.28104</v>
+      </c>
+      <c r="N6" t="n">
+        <v>-0.1610400000000001</v>
+      </c>
+      <c r="O6" t="b">
+        <v>0</v>
+      </c>
+      <c r="P6" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>-0.07594000000000001</v>
+      </c>
+      <c r="R6" t="n">
+        <v>-0.17134</v>
+      </c>
+      <c r="S6" t="b">
+        <v>0</v>
+      </c>
+      <c r="T6" t="b">
         <v>0</v>
       </c>
     </row>
@@ -745,36 +866,54 @@
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.11622</v>
+        <v>-0.1181</v>
       </c>
       <c r="E7" t="n">
-        <v>0.02619116263169698</v>
+        <v>0.02743000182282166</v>
       </c>
       <c r="F7" t="n">
-        <v>0.15284</v>
+        <v>0.15142</v>
       </c>
       <c r="G7" t="n">
-        <v>0.04456448137250113</v>
+        <v>0.01625629108991347</v>
       </c>
       <c r="H7" t="n">
-        <v>69.40000000000001</v>
+        <v>70</v>
       </c>
       <c r="I7" t="n">
-        <v>0.9333</v>
+        <v>0.7905</v>
       </c>
       <c r="J7" t="n">
-        <v>0.9571</v>
+        <v>0.7714</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.04952</v>
+        <v>0.181</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.80426</v>
-      </c>
-      <c r="M7" t="b">
-        <v>0</v>
-      </c>
-      <c r="N7" t="b">
+        <v>0.5143</v>
+      </c>
+      <c r="M7" t="n">
+        <v>-0.9086</v>
+      </c>
+      <c r="N7" t="n">
+        <v>-0.61998</v>
+      </c>
+      <c r="O7" t="b">
+        <v>0</v>
+      </c>
+      <c r="P7" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>-0.2991</v>
+      </c>
+      <c r="R7" t="n">
+        <v>-0.36288</v>
+      </c>
+      <c r="S7" t="b">
+        <v>0</v>
+      </c>
+      <c r="T7" t="b">
         <v>0</v>
       </c>
     </row>
@@ -793,37 +932,55 @@
         <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>0.3441</v>
+        <v>0.30258</v>
       </c>
       <c r="E8" t="n">
-        <v>0.03457766620233355</v>
+        <v>0.02176710821400032</v>
       </c>
       <c r="F8" t="n">
-        <v>0.56308</v>
+        <v>0.5446</v>
       </c>
       <c r="G8" t="n">
-        <v>0.02411445624516546</v>
+        <v>0.02060909993182623</v>
       </c>
       <c r="H8" t="n">
-        <v>63.6</v>
+        <v>65</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0974</v>
+        <v>0.1795</v>
       </c>
       <c r="J8" t="n">
-        <v>0.2923</v>
+        <v>0.3231</v>
       </c>
       <c r="K8" t="n">
-        <v>0.2467</v>
+        <v>0.4667</v>
       </c>
       <c r="L8" t="n">
-        <v>0.27078</v>
-      </c>
-      <c r="M8" t="b">
+        <v>0.7231</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.12308</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.2215</v>
+      </c>
+      <c r="O8" t="b">
         <v>1</v>
       </c>
-      <c r="N8" t="b">
+      <c r="P8" t="b">
         <v>1</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>-0.16412</v>
+      </c>
+      <c r="R8" t="n">
+        <v>-0.1785</v>
+      </c>
+      <c r="S8" t="b">
+        <v>0</v>
+      </c>
+      <c r="T8" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -841,37 +998,55 @@
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>0.76668</v>
+        <v>0.78002</v>
       </c>
       <c r="E9" t="n">
-        <v>0.01758229222826196</v>
+        <v>0.01215944077661469</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7933399999999999</v>
+        <v>0.77668</v>
       </c>
       <c r="G9" t="n">
-        <v>0.02237561172348141</v>
+        <v>0.01488663830419749</v>
       </c>
       <c r="H9" t="n">
         <v>60</v>
       </c>
       <c r="I9" t="n">
-        <v>0.8</v>
+        <v>0.7667</v>
       </c>
       <c r="J9" t="n">
-        <v>0.85</v>
+        <v>0.8167</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.03332000000000002</v>
+        <v>0.5</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.05666000000000004</v>
-      </c>
-      <c r="M9" t="b">
-        <v>0</v>
-      </c>
-      <c r="N9" t="b">
-        <v>0</v>
+        <v>0.7167</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.01332</v>
+      </c>
+      <c r="N9" t="n">
+        <v>-0.04001999999999994</v>
+      </c>
+      <c r="O9" t="b">
+        <v>1</v>
+      </c>
+      <c r="P9" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.28002</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0.05998000000000003</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -889,36 +1064,54 @@
         <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>0.2724799999999999</v>
+        <v>0.23418</v>
       </c>
       <c r="E10" t="n">
-        <v>0.03976590247938552</v>
+        <v>0.04030169971601694</v>
       </c>
       <c r="F10" t="n">
-        <v>0.47386</v>
+        <v>0.46462</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0207179390866949</v>
+        <v>0.04270564365514238</v>
       </c>
       <c r="H10" t="n">
         <v>195</v>
       </c>
       <c r="I10" t="n">
-        <v>0.6137</v>
+        <v>0.5795</v>
       </c>
       <c r="J10" t="n">
-        <v>0.7026</v>
+        <v>0.6359</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.3412200000000001</v>
+        <v>0.3744</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.22874</v>
-      </c>
-      <c r="M10" t="b">
-        <v>0</v>
-      </c>
-      <c r="N10" t="b">
+        <v>0.6462</v>
+      </c>
+      <c r="M10" t="n">
+        <v>-0.34532</v>
+      </c>
+      <c r="N10" t="n">
+        <v>-0.17128</v>
+      </c>
+      <c r="O10" t="b">
+        <v>0</v>
+      </c>
+      <c r="P10" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>-0.14022</v>
+      </c>
+      <c r="R10" t="n">
+        <v>-0.18158</v>
+      </c>
+      <c r="S10" t="b">
+        <v>0</v>
+      </c>
+      <c r="T10" t="b">
         <v>0</v>
       </c>
     </row>
@@ -937,36 +1130,54 @@
         <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>0.26474</v>
+        <v>0.2019</v>
       </c>
       <c r="E11" t="n">
-        <v>0.05144806118795925</v>
+        <v>0.07041697238592412</v>
       </c>
       <c r="F11" t="n">
-        <v>0.46856</v>
+        <v>0.40288</v>
       </c>
       <c r="G11" t="n">
-        <v>0.03697793936930504</v>
+        <v>0.05091750190258747</v>
       </c>
       <c r="H11" t="n">
         <v>70</v>
       </c>
       <c r="I11" t="n">
-        <v>0.9333</v>
+        <v>0.7905</v>
       </c>
       <c r="J11" t="n">
-        <v>0.9571</v>
+        <v>0.7714</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.66856</v>
+        <v>0.181</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.48854</v>
-      </c>
-      <c r="M11" t="b">
-        <v>0</v>
-      </c>
-      <c r="N11" t="b">
+        <v>0.5143</v>
+      </c>
+      <c r="M11" t="n">
+        <v>-0.5886</v>
+      </c>
+      <c r="N11" t="n">
+        <v>-0.36852</v>
+      </c>
+      <c r="O11" t="b">
+        <v>0</v>
+      </c>
+      <c r="P11" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.02090000000000003</v>
+      </c>
+      <c r="R11" t="n">
+        <v>-0.11142</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="b">
         <v>0</v>
       </c>
     </row>
@@ -985,37 +1196,55 @@
         <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.04820000000000001</v>
+        <v>-0.0728</v>
       </c>
       <c r="E12" t="n">
-        <v>0.07519075741073501</v>
+        <v>0.08127493463547049</v>
       </c>
       <c r="F12" t="n">
-        <v>0.30462</v>
+        <v>0.3261599999999999</v>
       </c>
       <c r="G12" t="n">
-        <v>0.02754835748279741</v>
+        <v>0.07082656987317684</v>
       </c>
       <c r="H12" t="n">
         <v>65</v>
       </c>
       <c r="I12" t="n">
-        <v>0.0974</v>
+        <v>0.1795</v>
       </c>
       <c r="J12" t="n">
-        <v>0.2923</v>
+        <v>0.3231</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.1456</v>
+        <v>0.4667</v>
       </c>
       <c r="L12" t="n">
-        <v>0.01232</v>
-      </c>
-      <c r="M12" t="b">
-        <v>0</v>
-      </c>
-      <c r="N12" t="b">
+        <v>0.7231</v>
+      </c>
+      <c r="M12" t="n">
+        <v>-0.2523</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.003059999999999952</v>
+      </c>
+      <c r="O12" t="b">
+        <v>0</v>
+      </c>
+      <c r="P12" t="b">
         <v>1</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>-0.5395</v>
+      </c>
+      <c r="R12" t="n">
+        <v>-0.39694</v>
+      </c>
+      <c r="S12" t="b">
+        <v>0</v>
+      </c>
+      <c r="T12" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1033,36 +1262,54 @@
         <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>0.6289</v>
+        <v>0.60442</v>
       </c>
       <c r="E13" t="n">
-        <v>0.03567688327194515</v>
+        <v>0.06012713197883297</v>
       </c>
       <c r="F13" t="n">
-        <v>0.6633600000000001</v>
+        <v>0.68668</v>
       </c>
       <c r="G13" t="n">
-        <v>0.02980399302107016</v>
+        <v>0.05056789495322107</v>
       </c>
       <c r="H13" t="n">
         <v>60</v>
       </c>
       <c r="I13" t="n">
-        <v>0.8</v>
+        <v>0.7667</v>
       </c>
       <c r="J13" t="n">
-        <v>0.85</v>
+        <v>0.8167</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.1711</v>
+        <v>0.5</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.1866399999999999</v>
-      </c>
-      <c r="M13" t="b">
-        <v>0</v>
-      </c>
-      <c r="N13" t="b">
+        <v>0.7167</v>
+      </c>
+      <c r="M13" t="n">
+        <v>-0.1622800000000001</v>
+      </c>
+      <c r="N13" t="n">
+        <v>-0.13002</v>
+      </c>
+      <c r="O13" t="b">
+        <v>0</v>
+      </c>
+      <c r="P13" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0.10442</v>
+      </c>
+      <c r="R13" t="n">
+        <v>-0.03002000000000005</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1081,36 +1328,54 @@
         <v>5</v>
       </c>
       <c r="D14" t="n">
-        <v>0.2082</v>
+        <v>0.14736</v>
       </c>
       <c r="E14" t="n">
-        <v>0.03662335320529784</v>
+        <v>0.0276369860874879</v>
       </c>
       <c r="F14" t="n">
-        <v>0.46566</v>
+        <v>0.43898</v>
       </c>
       <c r="G14" t="n">
-        <v>0.01557459469777624</v>
+        <v>0.02366425574574446</v>
       </c>
       <c r="H14" t="n">
         <v>195</v>
       </c>
       <c r="I14" t="n">
-        <v>0.6137</v>
+        <v>0.5795</v>
       </c>
       <c r="J14" t="n">
-        <v>0.7026</v>
+        <v>0.6359</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.4055</v>
+        <v>0.3744</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.23694</v>
-      </c>
-      <c r="M14" t="b">
-        <v>0</v>
-      </c>
-      <c r="N14" t="b">
+        <v>0.6462</v>
+      </c>
+      <c r="M14" t="n">
+        <v>-0.43214</v>
+      </c>
+      <c r="N14" t="n">
+        <v>-0.19692</v>
+      </c>
+      <c r="O14" t="b">
+        <v>0</v>
+      </c>
+      <c r="P14" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>-0.22704</v>
+      </c>
+      <c r="R14" t="n">
+        <v>-0.20722</v>
+      </c>
+      <c r="S14" t="b">
+        <v>0</v>
+      </c>
+      <c r="T14" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1129,36 +1394,54 @@
         <v>5</v>
       </c>
       <c r="D15" t="n">
-        <v>0.16002</v>
+        <v>0.05904</v>
       </c>
       <c r="E15" t="n">
-        <v>0.01564359293768538</v>
+        <v>0.07570464318653117</v>
       </c>
       <c r="F15" t="n">
-        <v>0.41142</v>
+        <v>0.35428</v>
       </c>
       <c r="G15" t="n">
-        <v>0.04563767084328473</v>
+        <v>0.08884842148288286</v>
       </c>
       <c r="H15" t="n">
         <v>70</v>
       </c>
       <c r="I15" t="n">
-        <v>0.9333</v>
+        <v>0.7905</v>
       </c>
       <c r="J15" t="n">
-        <v>0.9571</v>
+        <v>0.7714</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.77328</v>
+        <v>0.181</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.5456799999999999</v>
-      </c>
-      <c r="M15" t="b">
-        <v>0</v>
-      </c>
-      <c r="N15" t="b">
+        <v>0.5143</v>
+      </c>
+      <c r="M15" t="n">
+        <v>-0.73146</v>
+      </c>
+      <c r="N15" t="n">
+        <v>-0.41712</v>
+      </c>
+      <c r="O15" t="b">
+        <v>0</v>
+      </c>
+      <c r="P15" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>-0.12196</v>
+      </c>
+      <c r="R15" t="n">
+        <v>-0.16002</v>
+      </c>
+      <c r="S15" t="b">
+        <v>0</v>
+      </c>
+      <c r="T15" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1177,37 +1460,55 @@
         <v>5</v>
       </c>
       <c r="D16" t="n">
-        <v>0.23076</v>
+        <v>0.14872</v>
       </c>
       <c r="E16" t="n">
-        <v>0.0588991765647025</v>
+        <v>0.04645855141951802</v>
       </c>
       <c r="F16" t="n">
-        <v>0.52</v>
+        <v>0.47384</v>
       </c>
       <c r="G16" t="n">
-        <v>0.03334951274006864</v>
+        <v>0.02958611160663057</v>
       </c>
       <c r="H16" t="n">
         <v>65</v>
       </c>
       <c r="I16" t="n">
-        <v>0.0974</v>
+        <v>0.1795</v>
       </c>
       <c r="J16" t="n">
-        <v>0.2923</v>
+        <v>0.3231</v>
       </c>
       <c r="K16" t="n">
-        <v>0.13336</v>
+        <v>0.4667</v>
       </c>
       <c r="L16" t="n">
-        <v>0.2277</v>
-      </c>
-      <c r="M16" t="b">
+        <v>0.7231</v>
+      </c>
+      <c r="M16" t="n">
+        <v>-0.03077999999999997</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0.15074</v>
+      </c>
+      <c r="O16" t="b">
+        <v>0</v>
+      </c>
+      <c r="P16" t="b">
         <v>1</v>
       </c>
-      <c r="N16" t="b">
-        <v>1</v>
+      <c r="Q16" t="n">
+        <v>-0.31798</v>
+      </c>
+      <c r="R16" t="n">
+        <v>-0.2492599999999999</v>
+      </c>
+      <c r="S16" t="b">
+        <v>0</v>
+      </c>
+      <c r="T16" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1225,36 +1526,54 @@
         <v>5</v>
       </c>
       <c r="D17" t="n">
-        <v>0.24</v>
+        <v>0.2489</v>
       </c>
       <c r="E17" t="n">
-        <v>0.08225712735076517</v>
+        <v>0.02560624923724674</v>
       </c>
       <c r="F17" t="n">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="G17" t="n">
-        <v>0.04773772093428844</v>
+        <v>0.01180868324581536</v>
       </c>
       <c r="H17" t="n">
         <v>60</v>
       </c>
       <c r="I17" t="n">
-        <v>0.8</v>
+        <v>0.7667</v>
       </c>
       <c r="J17" t="n">
-        <v>0.85</v>
+        <v>0.8167</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.3799999999999999</v>
-      </c>
-      <c r="M17" t="b">
-        <v>0</v>
-      </c>
-      <c r="N17" t="b">
+        <v>0.7167</v>
+      </c>
+      <c r="M17" t="n">
+        <v>-0.5178</v>
+      </c>
+      <c r="N17" t="n">
+        <v>-0.3167</v>
+      </c>
+      <c r="O17" t="b">
+        <v>0</v>
+      </c>
+      <c r="P17" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>-0.2511</v>
+      </c>
+      <c r="R17" t="n">
+        <v>-0.2167</v>
+      </c>
+      <c r="S17" t="b">
+        <v>0</v>
+      </c>
+      <c r="T17" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1314,10 +1633,10 @@
         <v>70</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.219047619047619</v>
+        <v>-0.1714285714285714</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1</v>
+        <v>0.1428571428571429</v>
       </c>
     </row>
     <row r="3">
@@ -1335,10 +1654,10 @@
         <v>70</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.219047619047619</v>
+        <v>-0.1714285714285714</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1</v>
+        <v>0.1428571428571429</v>
       </c>
     </row>
     <row r="4">
@@ -1356,10 +1675,10 @@
         <v>70</v>
       </c>
       <c r="D4" t="n">
-        <v>0.7047619047619048</v>
+        <v>0.6142857142857143</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8571428571428571</v>
+        <v>0.7857142857142857</v>
       </c>
     </row>
     <row r="5">
@@ -1377,10 +1696,10 @@
         <v>70</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1619047619047619</v>
+        <v>0.1666666666666666</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2714285714285714</v>
+        <v>0.369047619047619</v>
       </c>
     </row>
     <row r="6">
@@ -1398,10 +1717,10 @@
         <v>65</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4051282051282051</v>
+        <v>0.0358974358974359</v>
       </c>
       <c r="E6" t="n">
-        <v>0.6153846153846154</v>
+        <v>0.4025641025641026</v>
       </c>
     </row>
     <row r="7">
@@ -1419,10 +1738,10 @@
         <v>65</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3230769230769231</v>
+        <v>-0.06153846153846154</v>
       </c>
       <c r="E7" t="n">
-        <v>0.4615384615384616</v>
+        <v>0.323076923076923</v>
       </c>
     </row>
     <row r="8">
@@ -1440,10 +1759,10 @@
         <v>65</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8256410256410257</v>
+        <v>0.7948717948717948</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9230769230769231</v>
+        <v>0.8769230769230769</v>
       </c>
     </row>
     <row r="9">
@@ -1461,10 +1780,10 @@
         <v>65</v>
       </c>
       <c r="D9" t="n">
-        <v>0.8153846153846154</v>
+        <v>0.7897435897435897</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9076923076923077</v>
+        <v>0.8615384615384616</v>
       </c>
     </row>
     <row r="10">
@@ -1482,10 +1801,10 @@
         <v>60</v>
       </c>
       <c r="D10" t="n">
-        <v>0.7333333333333335</v>
+        <v>0.6888888888888889</v>
       </c>
       <c r="E10" t="n">
-        <v>0.75</v>
+        <v>0.7222222222222221</v>
       </c>
     </row>
     <row r="11">
@@ -1503,10 +1822,10 @@
         <v>60</v>
       </c>
       <c r="D11" t="n">
-        <v>0.7333333333333335</v>
+        <v>0.6888888888888889</v>
       </c>
       <c r="E11" t="n">
-        <v>0.75</v>
+        <v>0.7305555555555555</v>
       </c>
     </row>
     <row r="12">
@@ -1524,10 +1843,10 @@
         <v>60</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.1888888888888889</v>
+        <v>-0.1777777777777778</v>
       </c>
       <c r="E12" t="n">
-        <v>0.1833333333333333</v>
+        <v>0.1916666666666667</v>
       </c>
     </row>
     <row r="13">
@@ -1545,10 +1864,10 @@
         <v>60</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.3777777777777778</v>
+        <v>-0.35</v>
       </c>
       <c r="E13" t="n">
-        <v>0.2</v>
+        <v>0.2083333333333333</v>
       </c>
     </row>
   </sheetData>
@@ -1607,10 +1926,10 @@
         <v>65</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8256410256410257</v>
+        <v>0.7948717948717948</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9230769230769231</v>
+        <v>0.8769230769230769</v>
       </c>
     </row>
     <row r="3">
@@ -1628,10 +1947,10 @@
         <v>70</v>
       </c>
       <c r="D3" t="n">
-        <v>0.7047619047619048</v>
+        <v>0.6142857142857143</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8571428571428571</v>
+        <v>0.7857142857142857</v>
       </c>
     </row>
     <row r="4">
@@ -1649,10 +1968,949 @@
         <v>60</v>
       </c>
       <c r="D4" t="n">
-        <v>0.7333333333333335</v>
+        <v>0.6888888888888889</v>
       </c>
       <c r="E4" t="n">
-        <v>0.75</v>
+        <v>0.7305555555555555</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:O17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>n_runs_AE</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>n_pairs</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>n_nonzero</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>AE_mean</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>baseline_mean</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>diff</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>statistic</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>p_value</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>rank_biserial</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>p_holm</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>significant_holm</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>holm_family_size</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>gptoss</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>FixedDefault</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>tau</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E2" t="n">
+        <v>195</v>
+      </c>
+      <c r="F2" t="n">
+        <v>174</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.2341880341880342</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.5794871794871795</v>
+      </c>
+      <c r="I2" t="n">
+        <v>-0.3452991452991453</v>
+      </c>
+      <c r="J2" t="n">
+        <v>3316</v>
+      </c>
+      <c r="K2" t="n">
+        <v>1.039430597158424e-10</v>
+      </c>
+      <c r="L2" t="n">
+        <v>-0.56440065681445</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1.559145895737636e-09</v>
+      </c>
+      <c r="N2" t="b">
+        <v>1</v>
+      </c>
+      <c r="O2" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>gptoss</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>FixedDefault</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Top-1</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>5</v>
+      </c>
+      <c r="E3" t="n">
+        <v>195</v>
+      </c>
+      <c r="F3" t="n">
+        <v>144</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.4646153846153846</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.6358974358974359</v>
+      </c>
+      <c r="I3" t="n">
+        <v>-0.1712820512820513</v>
+      </c>
+      <c r="J3" t="n">
+        <v>3350.5</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.000178522394952922</v>
+      </c>
+      <c r="L3" t="n">
+        <v>-0.3581417624521073</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.001249656764670454</v>
+      </c>
+      <c r="N3" t="b">
+        <v>1</v>
+      </c>
+      <c r="O3" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>gptoss</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>NearestNeighbor</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>tau</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>5</v>
+      </c>
+      <c r="E4" t="n">
+        <v>195</v>
+      </c>
+      <c r="F4" t="n">
+        <v>172</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.2341880341880342</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.3743589743589744</v>
+      </c>
+      <c r="I4" t="n">
+        <v>-0.1401709401709402</v>
+      </c>
+      <c r="J4" t="n">
+        <v>5977</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.02529356595850657</v>
+      </c>
+      <c r="L4" t="n">
+        <v>-0.1965317919075145</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.05058713191701314</v>
+      </c>
+      <c r="N4" t="b">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>gptoss</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>NearestNeighbor</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Top-1</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>5</v>
+      </c>
+      <c r="E5" t="n">
+        <v>195</v>
+      </c>
+      <c r="F5" t="n">
+        <v>147</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.4646153846153846</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.6461538461538462</v>
+      </c>
+      <c r="I5" t="n">
+        <v>-0.1815384615384615</v>
+      </c>
+      <c r="J5" t="n">
+        <v>3327</v>
+      </c>
+      <c r="K5" t="n">
+        <v>4.004240568013924e-05</v>
+      </c>
+      <c r="L5" t="n">
+        <v>-0.3883066740209598</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.0003203392454411139</v>
+      </c>
+      <c r="N5" t="b">
+        <v>1</v>
+      </c>
+      <c r="O5" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>qwen</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>FixedDefault</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>tau</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>5</v>
+      </c>
+      <c r="E6" t="n">
+        <v>195</v>
+      </c>
+      <c r="F6" t="n">
+        <v>185</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.1473504273504273</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.5794871794871795</v>
+      </c>
+      <c r="I6" t="n">
+        <v>-0.4321367521367522</v>
+      </c>
+      <c r="J6" t="n">
+        <v>3454</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1.602005184919525e-12</v>
+      </c>
+      <c r="L6" t="n">
+        <v>-0.5984888113920372</v>
+      </c>
+      <c r="M6" t="n">
+        <v>2.563208295871241e-11</v>
+      </c>
+      <c r="N6" t="b">
+        <v>1</v>
+      </c>
+      <c r="O6" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>qwen</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>FixedDefault</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Top-1</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>5</v>
+      </c>
+      <c r="E7" t="n">
+        <v>195</v>
+      </c>
+      <c r="F7" t="n">
+        <v>167</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.4389743589743589</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.6358974358974359</v>
+      </c>
+      <c r="I7" t="n">
+        <v>-0.196923076923077</v>
+      </c>
+      <c r="J7" t="n">
+        <v>4438</v>
+      </c>
+      <c r="K7" t="n">
+        <v>3.548621274296505e-05</v>
+      </c>
+      <c r="L7" t="n">
+        <v>-0.3672654690618762</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.0003193759146866854</v>
+      </c>
+      <c r="N7" t="b">
+        <v>1</v>
+      </c>
+      <c r="O7" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>qwen</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>NearestNeighbor</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>tau</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>5</v>
+      </c>
+      <c r="E8" t="n">
+        <v>195</v>
+      </c>
+      <c r="F8" t="n">
+        <v>183</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.1473504273504273</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.3743589743589744</v>
+      </c>
+      <c r="I8" t="n">
+        <v>-0.227008547008547</v>
+      </c>
+      <c r="J8" t="n">
+        <v>5330</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1.66098943316757e-05</v>
+      </c>
+      <c r="L8" t="n">
+        <v>-0.3668329769541459</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.0001993187319801084</v>
+      </c>
+      <c r="N8" t="b">
+        <v>1</v>
+      </c>
+      <c r="O8" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>qwen</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>NearestNeighbor</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Top-1</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>5</v>
+      </c>
+      <c r="E9" t="n">
+        <v>195</v>
+      </c>
+      <c r="F9" t="n">
+        <v>160</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.4389743589743589</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.6461538461538462</v>
+      </c>
+      <c r="I9" t="n">
+        <v>-0.2071794871794872</v>
+      </c>
+      <c r="J9" t="n">
+        <v>3652</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1.870478723369979e-06</v>
+      </c>
+      <c r="L9" t="n">
+        <v>-0.4329192546583851</v>
+      </c>
+      <c r="M9" t="n">
+        <v>2.431622340380973e-05</v>
+      </c>
+      <c r="N9" t="b">
+        <v>1</v>
+      </c>
+      <c r="O9" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>deepseek</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>FixedDefault</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>tau</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>5</v>
+      </c>
+      <c r="E10" t="n">
+        <v>195</v>
+      </c>
+      <c r="F10" t="n">
+        <v>178</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.252991452991453</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.5794871794871795</v>
+      </c>
+      <c r="I10" t="n">
+        <v>-0.3264957264957265</v>
+      </c>
+      <c r="J10" t="n">
+        <v>3865.5</v>
+      </c>
+      <c r="K10" t="n">
+        <v>2.53773582272301e-09</v>
+      </c>
+      <c r="L10" t="n">
+        <v>-0.5147197288305819</v>
+      </c>
+      <c r="M10" t="n">
+        <v>3.552830151812214e-08</v>
+      </c>
+      <c r="N10" t="b">
+        <v>1</v>
+      </c>
+      <c r="O10" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>deepseek</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>FixedDefault</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Top-1</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>5</v>
+      </c>
+      <c r="E11" t="n">
+        <v>195</v>
+      </c>
+      <c r="F11" t="n">
+        <v>164</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.4830769230769231</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.6358974358974359</v>
+      </c>
+      <c r="I11" t="n">
+        <v>-0.1528205128205128</v>
+      </c>
+      <c r="J11" t="n">
+        <v>4983.5</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.003275419188556191</v>
+      </c>
+      <c r="L11" t="n">
+        <v>-0.2633407243163341</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.01310167675422476</v>
+      </c>
+      <c r="N11" t="b">
+        <v>1</v>
+      </c>
+      <c r="O11" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>deepseek</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>NearestNeighbor</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>tau</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>5</v>
+      </c>
+      <c r="E12" t="n">
+        <v>195</v>
+      </c>
+      <c r="F12" t="n">
+        <v>166</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.252991452991453</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.3743589743589744</v>
+      </c>
+      <c r="I12" t="n">
+        <v>-0.1213675213675214</v>
+      </c>
+      <c r="J12" t="n">
+        <v>5262</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.007094014698653285</v>
+      </c>
+      <c r="L12" t="n">
+        <v>-0.2407474208210086</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.02128204409595986</v>
+      </c>
+      <c r="N12" t="b">
+        <v>1</v>
+      </c>
+      <c r="O12" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>deepseek</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>NearestNeighbor</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Top-1</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>5</v>
+      </c>
+      <c r="E13" t="n">
+        <v>195</v>
+      </c>
+      <c r="F13" t="n">
+        <v>137</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.4830769230769231</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.6461538461538462</v>
+      </c>
+      <c r="I13" t="n">
+        <v>-0.1630769230769231</v>
+      </c>
+      <c r="J13" t="n">
+        <v>2782.5</v>
+      </c>
+      <c r="K13" t="n">
+        <v>2.729570298871321e-05</v>
+      </c>
+      <c r="L13" t="n">
+        <v>-0.4112980006347192</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.0002729570298871322</v>
+      </c>
+      <c r="N13" t="b">
+        <v>1</v>
+      </c>
+      <c r="O13" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>gemini</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>FixedDefault</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>tau</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>5</v>
+      </c>
+      <c r="E14" t="n">
+        <v>195</v>
+      </c>
+      <c r="F14" t="n">
+        <v>137</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.2984615384615385</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.5794871794871795</v>
+      </c>
+      <c r="I14" t="n">
+        <v>-0.281025641025641</v>
+      </c>
+      <c r="J14" t="n">
+        <v>2748.5</v>
+      </c>
+      <c r="K14" t="n">
+        <v>2.009013227721001e-05</v>
+      </c>
+      <c r="L14" t="n">
+        <v>-0.4184914841849148</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.0002209914550493101</v>
+      </c>
+      <c r="N14" t="b">
+        <v>1</v>
+      </c>
+      <c r="O14" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>gemini</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>FixedDefault</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Top-1</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>5</v>
+      </c>
+      <c r="E15" t="n">
+        <v>195</v>
+      </c>
+      <c r="F15" t="n">
+        <v>114</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.4748717948717948</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.6358974358974359</v>
+      </c>
+      <c r="I15" t="n">
+        <v>-0.161025641025641</v>
+      </c>
+      <c r="J15" t="n">
+        <v>2220</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0.001632434685402635</v>
+      </c>
+      <c r="L15" t="n">
+        <v>-0.3226544622425629</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.008162173427013177</v>
+      </c>
+      <c r="N15" t="b">
+        <v>1</v>
+      </c>
+      <c r="O15" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>gemini</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>NearestNeighbor</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>tau</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>5</v>
+      </c>
+      <c r="E16" t="n">
+        <v>195</v>
+      </c>
+      <c r="F16" t="n">
+        <v>132</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.2984615384615385</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.3743589743589744</v>
+      </c>
+      <c r="I16" t="n">
+        <v>-0.0758974358974359</v>
+      </c>
+      <c r="J16" t="n">
+        <v>3845.5</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0.2158723041617826</v>
+      </c>
+      <c r="L16" t="n">
+        <v>-0.1238323080428344</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.2158723041617826</v>
+      </c>
+      <c r="N16" t="b">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>gemini</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>NearestNeighbor</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Top-1</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>5</v>
+      </c>
+      <c r="E17" t="n">
+        <v>195</v>
+      </c>
+      <c r="F17" t="n">
+        <v>96</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.4748717948717948</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.6461538461538462</v>
+      </c>
+      <c r="I17" t="n">
+        <v>-0.1712820512820513</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1367.5</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0.0002519173754712348</v>
+      </c>
+      <c r="L17" t="n">
+        <v>-0.4125859106529209</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.001511504252827409</v>
+      </c>
+      <c r="N17" t="b">
+        <v>1</v>
+      </c>
+      <c r="O17" t="n">
+        <v>16</v>
       </c>
     </row>
   </sheetData>
